--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -143,7 +143,7 @@
     <t>weapons:22</t>
   </si>
   <si>
-    <t>"sprite":"weapons:22","y":24,"x":15</t>
+    <t>"sprite":"weapons:22","y":24,"x":15,"aim":45</t>
   </si>
   <si>
     <t>"type":"ranged","range":5,"atk":15</t>
@@ -166,7 +166,7 @@
     <t>weapons:26</t>
   </si>
   <si>
-    <t>"sprite":"weapons:26","y":-8,"x":15</t>
+    <t>"sprite":"weapons:26","y":-8,"x":15,"aim":45</t>
   </si>
   <si>
     <t>"type":"ranged","range":5,"atk":25</t>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="232">
   <si>
     <t>id</t>
   </si>
@@ -548,6 +548,20 @@
   <si>
     <t xml:space="preserve">"lab": "Lockpick",
 "des": "Used with the lockpicking skill to pick locks."</t>
+  </si>
+  <si>
+    <t>icons:200</t>
+  </si>
+  <si>
+    <t>"cps":1000,"useable":true</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"lab":"金幣",
+"des":"可兌換成金錢"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"lab":"Gold",
+"des":""</t>
   </si>
   <si>
     <t>raw_meat</t>
@@ -1769,7 +1783,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="21.375"/>
   <cols>
     <col min="1" max="1" width="17.75" style="1" customWidth="1"/>
@@ -1949,9 +1963,12 @@
       <c r="D9" s="1">
         <v>15</v>
       </c>
+      <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
         <v>149</v>
       </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
       <c r="I9" s="1" t="s">
         <v>154</v>
       </c>
@@ -1961,6 +1978,34 @@
       <c r="K9" s="1" t="s">
         <v>156</v>
       </c>
+    </row>
+    <row r="10" ht="60" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L10" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -2031,207 +2076,207 @@
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D3" s="1">
         <v>10</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D4" s="1">
         <v>15</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D5" s="1">
         <v>10</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D6" s="1">
         <v>15</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D8" s="1">
         <v>10</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D10" s="1">
         <v>10</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D11" s="1">
         <v>10</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D12" s="1">
         <v>5</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -2269,12 +2314,12 @@
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.25">
@@ -2324,7 +2369,7 @@
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.25">
@@ -2334,7 +2379,7 @@
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -2374,13 +2419,13 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>10</v>
@@ -2391,37 +2436,37 @@
     </row>
     <row r="3" ht="75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -2485,25 +2530,25 @@
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>125</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -2511,25 +2556,25 @@
     </row>
     <row r="5" ht="44.25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>125</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D5" s="1">
         <v>10</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
@@ -2575,7 +2620,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>9</v>
@@ -2589,28 +2634,28 @@
     </row>
     <row r="3" ht="49.5" customHeight="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D3" s="1">
         <v>100</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -70,7 +70,7 @@
     <t>weapons:3</t>
   </si>
   <si>
-    <t>"sprite":"weapons:3","y":22</t>
+    <t>"sprite":"weapons:3","y":22,"swing":{"aim":-45,"grip":{"x":3,"y":28}}</t>
   </si>
   <si>
     <t>"type":"melee","range":1,"atk":15</t>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -423,7 +423,7 @@
     <t>weapons:6</t>
   </si>
   <si>
-    <t>"sprite":"weapons:6","y":22</t>
+    <t>"sprite":"weapons:6","y":22,"swing":{"aim":-45,"grip":{"x":5,"y":23}}</t>
   </si>
   <si>
     <t>"cat_sub":["axe"]</t>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="237">
   <si>
     <t>id</t>
   </si>
@@ -730,6 +730,23 @@
   </si>
   <si>
     <t xml:space="preserve">"lab": "Pot",
+"des": ""</t>
+  </si>
+  <si>
+    <t>dummy</t>
+  </si>
+  <si>
+    <t>rogue</t>
+  </si>
+  <si>
+    <t>"device":{"class":"dummy"}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"lab":"木樁",
+"des":"練習攻擊用的木樁，可放置、可拿取"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"lab": "Training Dummy",
 "des": ""</t>
   </si>
   <si>
@@ -2314,12 +2331,12 @@
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.25">
@@ -2419,13 +2436,13 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>10</v>
@@ -2436,37 +2453,37 @@
     </row>
     <row r="3" ht="75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -2530,13 +2547,13 @@
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>125</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -2545,10 +2562,10 @@
         <v>185</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -2556,25 +2573,25 @@
     </row>
     <row r="5" ht="44.25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>125</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D5" s="1">
         <v>10</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
@@ -2658,9 +2675,29 @@
         <v>209</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="1"/>
-      <c r="F4" s="3"/>
+    <row r="4" ht="49.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D4" s="1">
+        <v>50</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>214</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -79,7 +79,7 @@
     <t xml:space="preserve">{"type":"mod", "key":"str",   "a":1},
 {"stage":"atk", "scope":"self",   "type":"mod",    "key":"acc",   "m":0.1},
 {"stage":"atk", "scope":"target", "type":"mod",    "key":"eva",   "m":-0.1},
-{"stage":"hit", "scope":"target", "type":"debuff", "chance":0.5,  "dur":1,    "id":"stun", "icon":"💫"},
+{"stage":"hit", "scope":"target", "type":"debuff", "ctrl":true, "chance":0.5,  "dur":1,    "id":"stun", "icon":"💫"},
 {"stage":"hit", "scope":"target", "type":"dot",    "a":-1,        "dur":3,    "id":"poison", "icon":"🩸"},
 {"stage":"hit", "scope":"target", "type":"dot",    "m":-0.1,        "dur":3,    "id":"fire", "icon":"🔥" },
 {"stage":"hit", "scope":"self",   "type":"action", "chance":0.25, "key":"hp", "m":0.25, "id":"lifesteal"},

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -80,7 +80,7 @@
 {"stage":"atk", "scope":"self",   "type":"mod",    "key":"acc",   "m":0.1},
 {"stage":"atk", "scope":"target", "type":"mod",    "key":"eva",   "m":-0.1},
 {"stage":"hit", "scope":"target", "type":"debuff", "ctrl":true, "chance":0.5,  "dur":1,    "id":"stun", "icon":"💫"},
-{"stage":"hit", "scope":"target", "type":"dot",    "a":-1,        "dur":3,    "id":"poison", "icon":"🩸"},
+{"stage":"hit", "scope":"target", "type":"dot",    "a":-1,        "dur":3,    "elm":"poison", "id":"poison", "icon":"☠️"},
 {"stage":"hit", "scope":"target", "type":"dot",    "m":-0.1,        "dur":3,    "id":"fire", "icon":"🔥" },
 {"stage":"hit", "scope":"self",   "type":"action", "chance":0.25, "key":"hp", "m":0.25, "id":"lifesteal"},
 {"stage":"hit", "scope":"self",   "type":"buff", "stack":1, "key":"str", "a":1, "dur":3, "id":"strong", "icon":"💪"}</t>
@@ -109,7 +109,7 @@
     <t>"type":"melee","range":1,"atk":5</t>
   </si>
   <si>
-    <t>{"stage":"hit","scope":"target","type":"dot","a":-1,"dur":5,"stack":3,"elm":"poison","id":"posion", "icon":"☠️"}</t>
+    <t>{"stage":"hit","scope":"target","type":"dot","a":-1,"dur":5,"stack":3,"elm":"poison","id":"poison", "icon":"☠️"}</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"焠毒短劍",

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="235">
   <si>
     <t>id</t>
   </si>
@@ -47,9 +47,6 @@
   </si>
   <si>
     <t>effects</t>
-  </si>
-  <si>
-    <t>procs</t>
   </si>
   <si>
     <t>_others</t>
@@ -81,12 +78,9 @@
 {"stage":"atk", "scope":"target", "type":"mod",    "key":"eva",   "m":-0.1},
 {"stage":"hit", "scope":"target", "type":"debuff", "ctrl":true, "chance":0.5,  "dur":1,    "id":"stun", "icon":"💫"},
 {"stage":"hit", "scope":"target", "type":"dot",    "a":-1,        "dur":3,    "elm":"poison", "id":"poison", "icon":"☠️"},
-{"stage":"hit", "scope":"target", "type":"dot",    "m":-0.1,        "dur":3,    "id":"fire", "icon":"🔥" },
+{"stage":"hit", "scope":"target", "type":"dot",    "m":-0.1,        "elm":"fire","dur":3,    "id":"burn","stack":3, "icon":"🔥" },
 {"stage":"hit", "scope":"self",   "type":"action", "chance":0.25, "key":"hp", "m":0.25, "id":"lifesteal"},
 {"stage":"hit", "scope":"self",   "type":"buff", "stack":1, "key":"str", "a":1, "dur":3, "id":"strong", "icon":"💪"}</t>
-  </si>
-  <si>
-    <t>{"cond":"attack","scope":"enemy","type":"dot","value":2,"dur":3,"icon":"icons:0","tag":"bleed"}</t>
   </si>
   <si>
     <t>"cat_sub":["sword"]</t>
@@ -1223,11 +1217,10 @@
     <col min="6" max="6" width="35.375" style="1" customWidth="1"/>
     <col min="7" max="7" width="28.625" style="1" customWidth="1"/>
     <col min="8" max="8" width="32.75" style="1" customWidth="1"/>
-    <col min="9" max="9" width="27" style="1" customWidth="1"/>
-    <col min="10" max="10" width="37.5" style="1" customWidth="1"/>
-    <col min="11" max="11" width="21.375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="28" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="21.375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="37.5" style="1" customWidth="1"/>
+    <col min="10" max="10" width="21.375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="28" style="1" customWidth="1"/>
+    <col min="12" max="16383" width="21.375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1264,162 +1257,156 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="3" ht="300" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="D3" s="1">
         <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D4" s="1">
         <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D5" s="1">
         <v>35</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D6" s="1">
         <v>35</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D7" s="1">
         <v>35</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
@@ -1427,83 +1414,83 @@
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="D9" s="1">
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="J9" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="K9" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D10" s="1">
         <v>20</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="K10" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D11" s="1">
         <v>30</v>
       </c>
       <c r="G11" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K11" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -1511,83 +1498,83 @@
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="D13" s="1">
         <v>20</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J13" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="K13" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D14" s="1">
         <v>40</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J14" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="K14" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D15" s="1">
         <v>60</v>
       </c>
       <c r="G15" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K15" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
@@ -1595,118 +1582,118 @@
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="D17" s="1">
         <v>10</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="K17" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D18" s="1">
         <v>10</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J18" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="K18" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="D19" s="1">
         <v>10</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J19" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="K19" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D20" s="1">
         <v>10</v>
       </c>
       <c r="E20" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J20" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="K20" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
@@ -1714,71 +1701,71 @@
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="D22" s="1">
         <v>10</v>
       </c>
+      <c r="J22" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="K22" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="D23" s="1">
         <v>10</v>
       </c>
+      <c r="J23" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="K23" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D26" s="1">
         <v>10</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J26" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G26" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J26" s="1" t="s">
+      <c r="K26" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -1843,157 +1830,157 @@
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="D3" s="1">
         <v>10</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="D4" s="1">
         <v>10</v>
       </c>
       <c r="I4" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="D6" s="1">
         <v>10</v>
       </c>
       <c r="I6" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D7" s="1">
         <v>10</v>
       </c>
       <c r="H7" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D8" s="1">
         <v>10</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D9" s="1">
         <v>15</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -2001,10 +1988,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -2014,13 +2001,13 @@
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="L10" s="1"/>
     </row>
@@ -2082,218 +2069,218 @@
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>163</v>
       </c>
       <c r="D3" s="1">
         <v>10</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D4" s="1">
         <v>15</v>
       </c>
       <c r="H4" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D5" s="1">
         <v>10</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D6" s="1">
         <v>15</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I6" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D8" s="1">
         <v>10</v>
       </c>
       <c r="I8" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D10" s="1">
         <v>10</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I10" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D11" s="1">
         <v>10</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D12" s="1">
         <v>5</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I12" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -2331,72 +2318,72 @@
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -2436,54 +2423,54 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3" ht="75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -2536,36 +2523,36 @@
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -2573,25 +2560,25 @@
     </row>
     <row r="5" ht="44.25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D5" s="1">
         <v>10</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
@@ -2637,66 +2624,66 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3" ht="49.5" customHeight="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>205</v>
       </c>
       <c r="D3" s="1">
         <v>100</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="4" ht="49.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D4" s="1">
         <v>50</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>214</v>
       </c>
     </row>
   </sheetData>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -52,10 +52,10 @@
     <t>_others</t>
   </si>
   <si>
-    <t>tw</t>
-  </si>
-  <si>
-    <t>us</t>
+    <t>zh-TW</t>
+  </si>
+  <si>
+    <t>en</t>
   </si>
   <si>
     <t>sword_01</t>
@@ -1206,7 +1206,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="21.375"/>
   <cols>
     <col min="1" max="1" width="11.75" style="1" customWidth="1"/>
@@ -1223,7 +1223,7 @@
     <col min="12" max="16383" width="21.375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="300" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" ht="300" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1290,7 +1290,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" ht="60" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>26</v>
       </c>
@@ -1351,7 +1351,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>31</v>
       </c>
@@ -1380,7 +1380,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>38</v>
       </c>
@@ -1412,7 +1412,7 @@
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
     </row>
-    <row r="9" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>43</v>
       </c>
@@ -1441,7 +1441,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>51</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>58</v>
       </c>
@@ -1496,7 +1496,7 @@
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
     </row>
-    <row r="13" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>63</v>
       </c>
@@ -1525,7 +1525,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>70</v>
       </c>
@@ -1554,7 +1554,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>76</v>
       </c>
@@ -1580,7 +1580,7 @@
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
     </row>
-    <row r="17" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>81</v>
       </c>
@@ -1609,7 +1609,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>89</v>
       </c>
@@ -1638,7 +1638,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>94</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>101</v>
       </c>
@@ -1699,7 +1699,7 @@
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
     </row>
-    <row r="22" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>106</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>111</v>
       </c>
@@ -1739,7 +1739,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>116</v>
       </c>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="216">
   <si>
     <t>id</t>
   </si>
@@ -52,10 +52,10 @@
     <t>_others</t>
   </si>
   <si>
-    <t>zh-TW</t>
-  </si>
-  <si>
-    <t>en</t>
+    <t>lab</t>
+  </si>
+  <si>
+    <t>des</t>
   </si>
   <si>
     <t>sword_01</t>
@@ -86,12 +86,10 @@
     <t>"cat_sub":["sword"]</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"匕首",
-"des":"常用近戰武器"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Ordinary knife",
-"des":""</t>
+    <t>匕首</t>
+  </si>
+  <si>
+    <t>常用近戰武器</t>
   </si>
   <si>
     <t>sword_02</t>
@@ -106,12 +104,10 @@
     <t>{"stage":"hit","scope":"target","type":"dot","a":-1,"dur":5,"stack":3,"elm":"poison","id":"poison", "icon":"☠️"}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"焠毒短劍",
-"des":"用毒液浸泡過的短劍，可使目標中毒"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Iron Sword",
-"des":""</t>
+    <t>焠毒短劍</t>
+  </si>
+  <si>
+    <t>用毒液浸泡過的短劍，可使目標中毒</t>
   </si>
   <si>
     <t>sword_03</t>
@@ -123,12 +119,10 @@
     <t>"type":"melee","range":1,"atk":35</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"鋼劍",
-"des":""</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Steel Sword",
-"des":""</t>
+    <t>鋼劍</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>bow_01</t>
@@ -146,12 +140,7 @@
     <t>"cat_sub":["bow"]</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"弓",
-"des":""</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Bow",
-"des":""</t>
+    <t>弓</t>
   </si>
   <si>
     <t>bow_02</t>
@@ -166,8 +155,7 @@
     <t>"type":"ranged","range":5,"atk":25</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"高級弓",
-"des":""</t>
+    <t>高級弓</t>
   </si>
   <si>
     <t>helmet_01</t>
@@ -188,12 +176,7 @@
     <t>"def":10</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"草帽",
-"des":""</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Straw hat",
-"des":""</t>
+    <t>草帽</t>
   </si>
   <si>
     <t>helmet_02</t>
@@ -211,12 +194,7 @@
     <t>"def":20</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"麻布帽",
-"des":""</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Linen hat",
-"des":""</t>
+    <t>麻布帽</t>
   </si>
   <si>
     <t>helmet_03</t>
@@ -228,12 +206,7 @@
     <t>"def":30</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"皮帽",
-"des":""</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Leather hat",
-"des":""</t>
+    <t>皮帽</t>
   </si>
   <si>
     <t>chest_01</t>
@@ -251,12 +224,7 @@
     <t>"sprite":"cloth-armor","scale":0.25</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"草衣",
-"des":""</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Grass Clothes",
-"des":""</t>
+    <t>草衣</t>
   </si>
   <si>
     <t>chest_02</t>
@@ -271,12 +239,7 @@
     <t>"sprite":"leather-armor","scale":0.25</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"麻布衣",
-"des":""</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Linen Clothes",
-"des":""</t>
+    <t>麻布衣</t>
   </si>
   <si>
     <t>chest_03</t>
@@ -288,12 +251,7 @@
     <t>"def":40</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"皮衣",
-"des":""</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Leather",
-"des":""</t>
+    <t>皮衣</t>
   </si>
   <si>
     <t>gloves_01</t>
@@ -314,12 +272,7 @@
     <t>"def":5</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"手套",
-"des":""</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Gloves",
-"des":""</t>
+    <t>手套</t>
   </si>
   <si>
     <t>gloves_02</t>
@@ -334,8 +287,7 @@
     <t>"sprite":"leather-gloves","scale":0.25</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"高級手套",
-"des":""</t>
+    <t>高級手套</t>
   </si>
   <si>
     <t>boots_01</t>
@@ -353,12 +305,7 @@
     <t>"sprite":"cloth-boots","scale":0.25</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"靴子",
-"des":""</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Boots",
-"des":""</t>
+    <t>靴子</t>
   </si>
   <si>
     <t>boots_02</t>
@@ -373,8 +320,7 @@
     <t>"sprite":"leather-boots","scale":0.25</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"高級靴子",
-"des":""</t>
+    <t>高級靴子</t>
   </si>
   <si>
     <t>neck_01</t>
@@ -386,12 +332,7 @@
     <t>icons:134</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"項鍊",
-"des":""</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Necklace",
-"des":""</t>
+    <t>項鍊</t>
   </si>
   <si>
     <t>ring_01</t>
@@ -403,12 +344,7 @@
     <t>icons:132</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"戒子",
-"des":""</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Ring",
-"des":""</t>
+    <t>戒子</t>
   </si>
   <si>
     <t>axe_01</t>
@@ -423,12 +359,7 @@
     <t>"cat_sub":["axe"]</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"斧頭",
-"des":""</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Axe",
-"des":""</t>
+    <t>斧頭</t>
   </si>
   <si>
     <t>iron</t>
@@ -440,12 +371,7 @@
     <t>icons:273</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"鐵礦",
-"des":"鐵礦"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Iron ore",
-"des":""</t>
+    <t>鐵礦</t>
   </si>
   <si>
     <t>bag</t>
@@ -460,12 +386,10 @@
     <t>"storage":12</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"背包",
-"des":"可以裝物品"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Bag",
-"des":""</t>
+    <t>背包</t>
+  </si>
+  <si>
+    <t>可以裝物品</t>
   </si>
   <si>
     <t>torch</t>
@@ -481,12 +405,10 @@
 "light":{"color":16755200,"radius":300}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"火把",
-"des":"可以照明"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Torch",
-"des":""</t>
+    <t>火把</t>
+  </si>
+  <si>
+    <t>可以照明</t>
   </si>
   <si>
     <t>bottle</t>
@@ -502,12 +424,10 @@
 "capacity":10,"dft":3</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"水壺",
-"des":"可以裝水"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Bottle",
-"des":""</t>
+    <t>水壺</t>
+  </si>
+  <si>
+    <t>可以裝水</t>
   </si>
   <si>
     <t>key_0000</t>
@@ -519,12 +439,10 @@
     <t>"scale":0.5</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"鑰匙",
-"des":"可以開鎖"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"key",
-"des":""</t>
+    <t>鑰匙</t>
+  </si>
+  <si>
+    <t>可以開鎖</t>
   </si>
   <si>
     <t>lockpick</t>
@@ -536,12 +454,10 @@
     <t>"times":3</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"開鎖工具",
-"des":"開鎖的工具，需搭配開鎖技能，開鎖失敗會減少使用次數"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab": "Lockpick",
-"des": "Used with the lockpicking skill to pick locks."</t>
+    <t>開鎖工具</t>
+  </si>
+  <si>
+    <t>開鎖的工具，需搭配開鎖技能，開鎖失敗會減少使用次數</t>
   </si>
   <si>
     <t>icons:200</t>
@@ -550,12 +466,10 @@
     <t>"cps":1000,"useable":true</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"金幣",
-"des":"可兌換成金錢"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Gold",
-"des":""</t>
+    <t>金幣</t>
+  </si>
+  <si>
+    <t>可兌換成金錢</t>
   </si>
   <si>
     <t>raw_meat</t>
@@ -574,12 +488,10 @@
 "cook":{"id":"cooked_meat"}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"生肉",
-"des":"可烹煮"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Raw meat",
-"des":""</t>
+    <t>生肉</t>
+  </si>
+  <si>
+    <t>可烹煮</t>
   </si>
   <si>
     <t>cooked_meat</t>
@@ -594,12 +506,7 @@
     <t>"useable":true</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"熟肉",
-"des":"熟肉"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Cooked meat",
-"des":""</t>
+    <t>熟肉</t>
   </si>
   <si>
     <t>raw_fish</t>
@@ -608,12 +515,7 @@
     <t>icons:259</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"生魚",
-"des":"可烹煮"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Raw fish",
-"des":""</t>
+    <t>生魚</t>
   </si>
   <si>
     <t>salt_baked_fish</t>
@@ -626,12 +528,7 @@
 "make":{"items":{"raw_fish":1, "salt":2}}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"鹽烤魚",
-"des":"鹽烤魚"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Salt-baked fish",
-"des":""</t>
+    <t>鹽烤魚</t>
   </si>
   <si>
     <t>salt</t>
@@ -643,12 +540,7 @@
     <t>"cps":10</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"鹽",
-"des":"鹽"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Salt",
-"des":""</t>
+    <t>鹽</t>
   </si>
   <si>
     <t>apple</t>
@@ -660,12 +552,10 @@
     <t>"cps":5,"useable":true</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"頻果",
-"des":"可食用"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Apple",
-"des":""</t>
+    <t>頻果</t>
+  </si>
+  <si>
+    <t>可食用</t>
   </si>
   <si>
     <t>grapes</t>
@@ -674,12 +564,7 @@
     <t>icons:229</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"葡萄",
-"des":"可食用"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Strawberry",
-"des":""</t>
+    <t>葡萄</t>
   </si>
   <si>
     <t>mushroom</t>
@@ -691,12 +576,7 @@
     <t>"cps":10,"useable":true</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"蘑菇",
-"des":"可食用"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Mushroom",
-"des":""</t>
+    <t>蘑菇</t>
   </si>
   <si>
     <t>bb</t>
@@ -719,12 +599,10 @@
     <t>"device":{"class":"pot"}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"鍋子",
-"des":"可烹煮食物"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab": "Pot",
-"des": ""</t>
+    <t>鍋子</t>
+  </si>
+  <si>
+    <t>可烹煮食物</t>
   </si>
   <si>
     <t>dummy</t>
@@ -736,12 +614,10 @@
     <t>"device":{"class":"dummy"}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"木樁",
-"des":"練習攻擊用的木樁，可放置、可拿取"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab": "Training Dummy",
-"des": ""</t>
+    <t>木樁</t>
+  </si>
+  <si>
+    <t>練習攻擊用的木樁，可放置、可拿取</t>
   </si>
   <si>
     <t>bb_view</t>
@@ -798,12 +674,10 @@
     <t>assets_spritesheet_v2_free/028.png</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"木材",
-"des":"有用的資源"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Wood",
-"des":""</t>
+    <t>木材</t>
+  </si>
+  <si>
+    <t>有用的資源</t>
   </si>
   <si>
     <t>plet</t>
@@ -815,12 +689,10 @@
     <t>"cps":5</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"毛皮",
-"des":"從動物身上剝下來、帶有毛髮的完整皮毛。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Plet",
-"des":""</t>
+    <t>毛皮</t>
+  </si>
+  <si>
+    <t>從動物身上剝下來、帶有毛髮的完整皮毛。</t>
   </si>
   <si>
     <t>CAT_ALL</t>
@@ -1377,36 +1249,36 @@
         <v>36</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D7" s="1">
         <v>35</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
@@ -1414,83 +1286,83 @@
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="D9" s="1">
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="J9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="K9" s="1" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D10" s="1">
         <v>20</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="K10" s="1" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D11" s="1">
         <v>30</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -1498,83 +1370,83 @@
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D13" s="1">
         <v>20</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D14" s="1">
         <v>40</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D15" s="1">
         <v>60</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
@@ -1582,118 +1454,118 @@
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="D17" s="1">
         <v>10</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>88</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="D18" s="1">
         <v>10</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>88</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D19" s="1">
         <v>10</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>100</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="D20" s="1">
         <v>10</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>100</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
@@ -1701,71 +1573,71 @@
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D22" s="1">
         <v>10</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>110</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="D23" s="1">
         <v>10</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>115</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="D26" s="1">
         <v>10</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>15</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>121</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1841,146 +1713,146 @@
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D3" s="1">
         <v>10</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="D4" s="1">
         <v>10</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="D6" s="1">
         <v>10</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="D7" s="1">
         <v>10</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="D8" s="1">
         <v>10</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="D9" s="1">
         <v>15</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -1988,10 +1860,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -2001,13 +1873,13 @@
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="L10" s="1"/>
     </row>
@@ -2080,207 +1952,207 @@
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="D3" s="1">
         <v>10</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="D4" s="1">
         <v>15</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="D5" s="1">
         <v>10</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="D6" s="1">
         <v>15</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="D8" s="1">
         <v>10</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="D10" s="1">
         <v>10</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="D11" s="1">
         <v>10</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="D12" s="1">
         <v>5</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -2318,12 +2190,12 @@
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
-        <v>233</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
-        <v>234</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.25">
@@ -2333,57 +2205,57 @@
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -2423,13 +2295,13 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>213</v>
+        <v>194</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>9</v>
@@ -2438,40 +2310,48 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" ht="75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="4" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" ht="60" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" ht="60" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="6" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" ht="45" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>223</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2534,25 +2414,25 @@
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -2560,25 +2440,25 @@
     </row>
     <row r="5" ht="44.25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>229</v>
+        <v>210</v>
       </c>
       <c r="D5" s="1">
         <v>10</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>232</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
@@ -2624,7 +2504,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>8</v>
@@ -2638,52 +2518,52 @@
     </row>
     <row r="3" ht="49.5" customHeight="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="D3" s="1">
         <v>100</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" ht="49.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="D4" s="1">
         <v>50</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="1" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
